--- a/data/Paper.xlsx
+++ b/data/Paper.xlsx
@@ -1,96 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samarthg/Documents/invoiceEditor/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EDDD70-CABB-544B-BC60-13CF0C98E15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="April" sheetId="1" r:id="rId1"/>
-    <sheet name="May" sheetId="2" r:id="rId2"/>
-    <sheet name="June" sheetId="3" r:id="rId3"/>
+    <sheet name="May" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="June" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="15">
-  <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Consumption Period</t>
-  </si>
-  <si>
-    <t>Utilisation (%)</t>
-  </si>
-  <si>
-    <t>Consumption (%)</t>
-  </si>
-  <si>
-    <t>Net Price</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>Jake</t>
-  </si>
-  <si>
-    <t>Jude</t>
-  </si>
-  <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -105,43 +47,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -429,57 +421,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>0.33</v>
-      </c>
-      <c r="F2">
-        <v>33.33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Period</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Usage (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Net Price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -488,186 +472,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Percentage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Usage (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Net Price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Period</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Utilisation (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption (%)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>0.32</v>
-      </c>
-      <c r="F2">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
+      <c r="K2" t="n">
         <v>0.33</v>
-      </c>
-      <c r="F2">
-        <v>33.33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>50</v>
-      </c>
-      <c r="C3">
-        <v>14</v>
-      </c>
-      <c r="D3">
-        <v>70</v>
-      </c>
-      <c r="E3">
-        <v>0.47</v>
-      </c>
-      <c r="F3">
-        <v>16.45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>140</v>
-      </c>
-      <c r="C4">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>85</v>
-      </c>
-      <c r="E4">
-        <v>0.4</v>
-      </c>
-      <c r="F4">
-        <v>47.6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>170</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>25</v>
-      </c>
-      <c r="E5">
-        <v>0.33</v>
-      </c>
-      <c r="F5">
-        <v>14.025</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/Paper.xlsx
+++ b/data/Paper.xlsx
@@ -2,23 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="May" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="June" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +26,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -47,23 +55,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,8 +463,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -442,7 +479,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Consumption Period</t>
+          <t>Consumption Percentage</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -460,9 +497,19 @@
           <t>Net Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
         </is>
       </c>
     </row>
@@ -477,8 +524,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -511,7 +558,7 @@
           <t>Net Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -523,53 +570,8 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Consumption Period</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Utilisation (%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Consumption (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>100</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.33</v>
+          <t>Invoiced</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Paper.xlsx
+++ b/data/Paper.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="May" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="June" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="June" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,52 +46,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -463,8 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -497,81 +459,243 @@
           <t>Net Price</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Customer Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Consumption Percentage</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Usage (%)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Consumption Duration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90.66666666666666</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Net Price</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Invoiced</t>
-        </is>
+      <c r="I7" t="n">
+        <v>186.3366666666666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>219.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/Paper.xlsx
+++ b/data/Paper.xlsx
@@ -1,96 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="June" sheetId="1" r:id="rId1"/>
+    <sheet name="June" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
-  <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Consumption Percentage</t>
-  </si>
-  <si>
-    <t>Usage (%)</t>
-  </si>
-  <si>
-    <t>Consumption Duration</t>
-  </si>
-  <si>
-    <t>Net Price</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Invoiced</t>
-  </si>
-  <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>CGST</t>
-  </si>
-  <si>
-    <t>SGST</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -105,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,159 +420,281 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Percentage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Usage (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Net Price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>250</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>500</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>0.47</v>
-      </c>
-      <c r="F2">
-        <v>23.5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>0.5</v>
-      </c>
-      <c r="F3">
-        <v>50</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
-        <v>250</v>
-      </c>
-      <c r="C4">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>0.47</v>
-      </c>
-      <c r="F4">
-        <v>22.17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="H6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>95.67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7">
-        <v>8.609999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8">
-        <v>8.609999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9">
-        <v>112.89</v>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Net Price</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>100.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>118.79</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>